--- a/MavenBook/src/test/resources/CustomerData.xlsx
+++ b/MavenBook/src/test/resources/CustomerData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="61">
   <si>
     <t>Salutation</t>
   </si>
@@ -126,100 +126,79 @@
     <t>Mobile No</t>
   </si>
   <si>
-    <t>Mr</t>
-  </si>
-  <si>
-    <t>Mathew</t>
+    <t>Saudi Riyal</t>
+  </si>
+  <si>
+    <t>Net 15</t>
+  </si>
+  <si>
+    <t>www.subin.fb.com</t>
+  </si>
+  <si>
+    <t>subin@x.com</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Software Testing</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Fname</t>
+  </si>
+  <si>
+    <t>Lname</t>
+  </si>
+  <si>
+    <t>contact1@test.com</t>
+  </si>
+  <si>
+    <t>Company Disp Name(Arabic)</t>
+  </si>
+  <si>
+    <t>9942000355</t>
+  </si>
+  <si>
+    <t>Contact Work Phone</t>
+  </si>
+  <si>
+    <t>9645567891</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>355458489378423</t>
+  </si>
+  <si>
+    <t>Contact FName</t>
+  </si>
+  <si>
+    <t>Contact LName</t>
+  </si>
+  <si>
+    <t>Contact Salutation</t>
+  </si>
+  <si>
+    <t>Vat Reg Customer</t>
+  </si>
+  <si>
+    <t>Non GCC Customer</t>
+  </si>
+  <si>
+    <t>subin.polosys@yahoo.com</t>
+  </si>
+  <si>
+    <t>subin.polosys2@yahoo.com</t>
   </si>
   <si>
     <t>VAT Registered</t>
   </si>
   <si>
-    <t>Saudi Riyal</t>
-  </si>
-  <si>
-    <t>Net 15</t>
-  </si>
-  <si>
-    <t>www.test12.com</t>
-  </si>
-  <si>
-    <t>www.subin.fb.com</t>
-  </si>
-  <si>
-    <t>subin@x.com</t>
-  </si>
-  <si>
-    <t>Tester</t>
-  </si>
-  <si>
-    <t>Software Testing</t>
-  </si>
-  <si>
-    <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>addrL1</t>
-  </si>
-  <si>
-    <t>Mecca Province</t>
-  </si>
-  <si>
-    <t>Addr L2</t>
-  </si>
-  <si>
-    <t>Addr L3</t>
-  </si>
-  <si>
-    <t>Meccah</t>
-  </si>
-  <si>
-    <t>Tree</t>
-  </si>
-  <si>
-    <t>Fname</t>
-  </si>
-  <si>
-    <t>Lname</t>
-  </si>
-  <si>
-    <t>contact1@test.com</t>
-  </si>
-  <si>
-    <t>Company Disp Name(Arabic)</t>
-  </si>
-  <si>
-    <t>9942000355</t>
-  </si>
-  <si>
-    <t>Contact Work Phone</t>
-  </si>
-  <si>
-    <t>9645567891</t>
-  </si>
-  <si>
-    <t>Mr.</t>
-  </si>
-  <si>
-    <t>Sujith</t>
-  </si>
-  <si>
-    <t>sujith.polosys@yahoo.com</t>
-  </si>
-  <si>
-    <t>sujith.polosys2@yahoo.com</t>
-  </si>
-  <si>
-    <t>355458489378423</t>
-  </si>
-  <si>
-    <t>Contact FName</t>
-  </si>
-  <si>
-    <t>Contact LName</t>
-  </si>
-  <si>
-    <t>Contact Salutation</t>
+    <t>Non Gcc</t>
   </si>
 </sst>
 </file>
@@ -635,11 +614,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" style="1" customWidth="1"/>
@@ -682,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>5</v>
@@ -741,78 +720,121 @@
     </row>
     <row r="2" spans="1:24" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="K2" s="14">
         <v>100</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="14">
         <v>100</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="14">
+        <v>100</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="Q3" s="14"/>
+      <c r="O3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>100</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:24" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="I4" s="14"/>
@@ -859,21 +881,18 @@
     <row r="10" spans="1:24" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
       <c r="M10" s="14"/>
       <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:24" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
       <c r="M11" s="14"/>
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="1:24" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
       <c r="M12" s="14"/>
       <c r="Q12" s="14"/>
     </row>
@@ -913,32 +932,23 @@
       <c r="M18" s="14"/>
       <c r="Q18" s="14"/>
     </row>
-    <row r="19" spans="9:17" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="Q19" s="14"/>
-    </row>
-    <row r="20" spans="9:17" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="Q20" s="14"/>
-    </row>
-    <row r="21" spans="9:17" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="Q21" s="14"/>
+    <row r="19" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="J19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="Q19" s="15"/>
+    </row>
+    <row r="20" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="J20" s="15"/>
+      <c r="Q20" s="15"/>
+    </row>
+    <row r="21" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="9:17" x14ac:dyDescent="0.2">
       <c r="J22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="Q22" s="15"/>
     </row>
     <row r="23" spans="9:17" x14ac:dyDescent="0.2">
       <c r="J23" s="15"/>
-      <c r="Q23" s="15"/>
     </row>
     <row r="24" spans="9:17" x14ac:dyDescent="0.2">
       <c r="J24" s="15"/>
@@ -948,23 +958,16 @@
     </row>
     <row r="26" spans="9:17" x14ac:dyDescent="0.2">
       <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="9:17" x14ac:dyDescent="0.2">
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="9:17" x14ac:dyDescent="0.2">
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="9:17" x14ac:dyDescent="0.2">
-      <c r="J29" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="H2" r:id="rId2"/>
+    <hyperlink ref="G3" r:id="rId3"/>
+    <hyperlink ref="H3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -1023,39 +1026,9 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="14">
-        <v>452102</v>
-      </c>
-      <c r="J2" s="14">
-        <v>6854127854</v>
-      </c>
-      <c r="K2" s="14">
-        <v>6875214655</v>
-      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="I3" s="14"/>
@@ -1173,19 +1146,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>34</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>35</v>
@@ -1193,16 +1166,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15">
         <v>4561320789</v>
@@ -1212,20 +1185,84 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
+      <c r="A3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="15">
+        <v>4561320789</v>
+      </c>
+      <c r="F3" s="15">
+        <v>3605412789</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
+      <c r="A4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="15">
+        <v>4561320789</v>
+      </c>
+      <c r="F4" s="15">
+        <v>3605412789</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="15">
+        <v>4561320789</v>
+      </c>
+      <c r="F5" s="15">
+        <v>3605412789</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="A6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="15">
+        <v>4561320789</v>
+      </c>
+      <c r="F6" s="15">
+        <v>3605412789</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E7" s="15"/>
